--- a/玄鸟统计结果.xlsx
+++ b/玄鸟统计结果.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,11 +443,4081 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>saila</t>
+          <t>大连锦程国际贸易有限公司</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>宁波合羽国际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>宁波致翔供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>青岛捷瀛船务有限公司</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>宁波全顺捷运物流有限公司</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>宁波速恒国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>宁波至华国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>宁波中景新程物流集团有限公司</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>中集世联达亚联国际物流有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>浙江明骏供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>浙江天时利蜻蜓供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>浙江泽惠供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>五朵金花运营中心</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>大连锦程国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>浙江某某国际货运代理有限公司 (演示)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>上海龙辕供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>上海旭华物流有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>宁波晴海国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>宁波鼎领国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>深圳凯高现代物流有限公司</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>安必快外贸综合服务（惠州）有限公司</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>浙江佳福国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>江苏常利来国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>联邦快递（中国）有限公司深圳分公司</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>江苏明美国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>宁波亿泓国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>深圳市中传国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>江苏纽生堂国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>江苏宏达通国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>惠州市巨航供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>深圳市博洋供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>深圳市格威达国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>常州鹏欣供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>深圳智中行国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>宁波乾洋国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>万集（宁波）供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>昆山贝尔通国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>安徽福沣国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>上海蕴鑫供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>宁波成一国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>上海简凯国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>安徽乐扬国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>无锡万航国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>浙江木牛流马供应链有限公司德清分公司</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>上海欣乐享供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>宁波鼎领国际物流有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>神轮（苏州）国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>昆山艾亘国际贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>宁波宁舟船务有限公司</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>宁波锦海供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>江苏欣拓国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>上海文鳐供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>宁波当曲科技有限公司</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>浙江繁简供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>宁波忻辰国际供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>宁波集达供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>安吉捷泰家居有限责任公司</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>浙江中非国际经贸港服务有限公司</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>杭州高新供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>宁波海瑞得国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>浙江君集国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>广州市路瑞供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>上海融强国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>南京唯派国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>杭州环宇国际货运有限公司</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>浙江天时利蜻蜓供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>上海青禾物流有限公司</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>广州福施湃乐电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>文誉供应链管理（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>重庆创辉国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>锦程国际物流集团武汉国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>上海金阳海悦供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>上海诺嘉国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>浙江至帆物流有限公司</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>安徽卓达国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>大连辉泓国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>华基国际物流（宁波）有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>佛山市永正大进出口有限公司</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>浙江嘉兴高通国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>浙江美川国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>上海衍旭物流有限公司</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>浙江双宇电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>安徽凯福佑国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>星东国际物流（宁波）有限公司</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>湖南西联捷运国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>上海美昊杰国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>上海贝莱蒂供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>嘉里大通物流有限公司湖北分公司</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>宁波中合供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>宁波瑞尚供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>青岛明通国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>宁波力朗供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>浙江跨运科技有限公司</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>宁波柏胜国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>浙江跨运供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>宁波甬兰国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>宁波汇洋国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>金华安睿国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>吔百国际贸易（广东）有限公司</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>宁波吉瑞国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>上海中善物流有限公司</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>锐链宁波</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>优信嘉运国际物流（苏州）有限公司</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>美设国际物流集团股份有限公司杭州分公司</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>宁波久瀚国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>深圳古瑞瓦特新能源有限公司</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>上海天兆国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>上海睿淼供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>领惠（上海）供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>上海丹吉士国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>上海寰美国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>上海海波物流有限公司</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>上海复易国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>融华智运国际物流（青岛）有限公司</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>宁波熙佳国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>上海大瀚国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>宁波得玛供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>深圳市航时运通国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>浩鸣国际物流代理有限公司</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>嘉兴环世国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>宁波寰航供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>诺得物流股份有限公司</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>江苏仁义多式联运有限公司</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>湖州安吉星辙国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>湖州恒众国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>浙江海舜供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>浙江扬程国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>浙江绍兴美力物流有限公司</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>博达供应链科技（宁波）有限公司</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>南京中腾物流有限公司</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>广州市骏亨国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>浙江阿啦丁国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>常州蓝湾国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>义乌美星国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>港拓（深圳）贸易有限公司</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>上海华原国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>诸暨市中创物流有限公司</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>合肥远洋国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>志存（宁波）供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>深圳百隆美亚国际货运代理有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>浙江泽惠供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>广州市卓志报关有限公司</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>大连万联供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>宁波陆洋国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>上海传鸿国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>上海陆启通国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>温州市鹿城区滨江晨夕货物运输服务部</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>上海协利物流有限公司</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>宁波田天供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>泽世国际货运代理（深圳）有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>宁波美晟国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>上海境港供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>浙江四港联动发展有限公司</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>浙江星驰国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>义乌市中超集装箱有限公司</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>宁波伊亲国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>浙江天熠国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>浙江多多马国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>湖州胜开供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>温州达丰国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>顺圆弘通物流集团有限公司</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>上海上楚供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>穰穰满仓（上海）供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>中集世联达亚联国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>上海卓之烁供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>安徽盛凯国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>丹时达供应链管理(上海)有限公司</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>上海汇恒国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>宁波鑫淼国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>安徽即联即用科技有限公司</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>宁波希澜供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>宁波市焕航物流有限公司</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>福建港运国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>青岛万家船务有限公司</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>浙江运到数字物流发展有限公司</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>上海樱美供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>嘉德运通（福州）国际货运代理有限公司厦门分公司</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>浙江纵深供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>中山市海迅捷运国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>天津瑞洋供应链管理服务有限公司</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>宁波观龙供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>港联捷（上海）物流科技有限公司</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>安徽兆洋国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>上海海木国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>安徽烁道国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>宁波华沃供应链科技有限公司</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>浙江新嘉国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>杭州海杭境通供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>浙江海金国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>上海舒雯国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>上海粤立申国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>宁波安洲国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>义乌友航国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>义乌市大程国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>宁波万时国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>深圳市顺云峰国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>宁波中沃日新国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>海宁吉佑佳国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>浙江喜航供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>浙江振昊供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>上海飞远物流有限公司</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>杭州卓远国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>宁波锦然国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>宁波速帆供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>上海秀登供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>宁波捷义国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>盟湾国际物流（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>浙江华世货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>宁波淳宏供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>安徽安商国际供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>宁波涵瑞供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>广东航桥国际物流股份有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>浙江智杰国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>温州灏璟国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>湖北快航国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>宁波乔山国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>深圳市运通报关有限公司</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>上海优一克国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>信达海新国际物流（大连）有限公司</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>浙江纺都国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>衢州市捷海国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>苏州德豹供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>福励物流科技（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>上海嘉其国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>南京上楚供应链有限责任公司</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>宁波天航国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>上海茂曦轩国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>宁波锦昌国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>宁波捷时进出口有限公司</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>江苏海丰国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>浙江嘉澜国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>江苏海航供应链管理服务有限公司</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>上海大展国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>上海升笙国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>海邦（江苏）国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>浙江海创国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>江苏航吉国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>宁波盛威国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>宁波联洋船务有限公司</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>宁波民亨国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>湖州易航国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>宁波大千国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>宁波路遥国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>浙江美升国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>宁波伟大联盟国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>杭州达升坤道国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>天津安海物流发展有限公司上海分公司</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>浙江锦鸿物流有限公司</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>浙江华凯供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>浙江佰度物流有限公司</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>浙江经茂国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>浙江韵昇航运有限公司</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>浙江福瑞鑫供应链服务有限公司</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>浙江凤起物流有限公司</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>昆山邦达国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>宁波鸿远国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>浙江翼港物流有限公司</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>宁波港泰国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>温州承运国际货运有限公司</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>浙江湖州华凯国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>宁波亦豪供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>义乌市源辉物流有限公司</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>浙江耐斯特国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>宁波竭诚国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>宁波顺圆物流有限公司</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>宁波中景国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>宁波博皓国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>宁波杰兰德国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>宁波优诺舟国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>浙江融易通企业服务有限公司</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>宁波希朗国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>宁波源联国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>杭州华意国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>宁波星赛蒂国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>浙江海盟国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>嘉兴祺达国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>杭州泛远国际物流股份有限公司</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>宁波志诺国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>浙江鑫骋物流有限公司</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>杭州金海岸国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>港捷（中国）国际货运有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>江苏天禄国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>浙江开瑞国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>杭州和邦国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>浙江锦睿国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>上海万年青国际物流有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>上海奥集国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>西格玛国际物流（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>浙江三石力供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>浙江天闳国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>上海义统国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>上海康芸物流发展有限公司</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>苏州鑫梦成物流有限公司</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>锦程国际物流集团上海国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>嘉兴伟诚国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>上海家林国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>大连海升国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>浙江禹洋国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>上海美凰国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>大连汇诚睿国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>海盟控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>宁波骝马供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>浙江长川物流有限公司</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>宁波和瀚国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>江苏嘉格国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>上海诺亚国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>宁波世纪泊洋国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>湖州振和供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>江苏新天国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>嘉兴麒成供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>上海聚翰船务有限公司</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>上海富天国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>宁波乐洲国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>浙江恒圣供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>宁波市联合大洋物流有限公司</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>上海全运货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>宁波骏联国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>江苏鑫博亚国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>飞力达供应链（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>天徽国际供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>南通金帆国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>常熟市华盛国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>安徽渡达国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>杭州至星国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>安徽海汐国际货运有限公司</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>上海枚一国际货物运输代理有限公司</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>深圳市集万国际货物运输有限公司</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>青岛舜安恒泰国际物流有限公司杭州分公司</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>上海羽嘉国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>格瑞德国际货运代理（苏州）有限公司</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>沃泰国际物流（宁波）有限公司</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>一席货运代理（金华）有限公司</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>上海久瀚国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>上海嘉赫国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>浙江胜马国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>中宏飞集国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>浙江锦诚国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>上海新新运国际物流有限公司杭州分公司</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>嘉兴中航国际货运代理股份有限公司</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>湖州天航国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>上海恒扬国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>嘉兴恒元国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>上海冠农国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>杭州港翔致昇国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>湖北航嘉国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>嘉兴锦诚国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>临海市正大国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>宁波美速嘉运国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>宁波终赢供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>宁波风速供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>宁波环翎国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>宁波鹏信国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>宁波腾海供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>宁波天拓泰世通国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>宁波腾辉国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>宁波凯腾国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>宁波无双供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>宁波亿天国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>宁波外运国际集装箱货运有限公司</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>宁波星皓国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>宁波路遥供应链科技（集团）有限公司</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>优尼科供应链（深圳）有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>仕巴伊努(杭州)供应链有限公司</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>昇冠(宁波)国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>上海金色物流有限公司</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>上海鸿茂国际物流有限公司宁波分公司</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>绍兴海隆国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>深圳市顺和盈货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>深圳市辰帆国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>深圳翰远国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>天津东时供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>台州源广达迅国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>咏耀船务（青岛）有限公司</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>中博润达物流(浙江)有限公司</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>宁波中创远合物流有限公司</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>青岛慧通世达国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>宁波君桥国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>宁波金仑国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>宁波怡升昌供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>宁波终赢供应链管理有限公司</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>上海恒汇达国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>绍兴柯桥红胜火纺织品有限公司</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>浙江海亮股份有限公司</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>宁波开万国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>青岛山建商贸有限公司</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>卓辰实业（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>宁波天美利进出口有限公司</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>宁波东曜电器有限公司</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>舟山晟利食品有限公司</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>西格玛国际物流（上海）有限公司</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>宁波来回转自动化工业有限公司</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>浙江海亮股份有限公司</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>中国邮政速递物流股份有限公司绍兴市分公司</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>杭州凤起国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>浙江你好国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>中国邮政速递物流股份有限公司衢州市分公司</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>浙江外代国际物流有限公司</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>浙江启胜国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>浙江聚航国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>浙江港盈科技有限公司</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>浙江金斯顿供应链集团有限公司</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>浙江省桐乡经济开发区管理委员会</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>浙江易鑫国际货运代理有限公司</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>智美通国际物流(深圳)有限公司</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>众翔供应链管理(浙江)有限公司</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>易豹网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>浙江海蛛网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>浙江运到数字物流发展有限公司</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
